--- a/test_data/plantilla_stock_inicial.xlsx
+++ b/test_data/plantilla_stock_inicial.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plantilla" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Plantilla" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -428,20 +428,25 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Recinto</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Talla</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Stock Mínimo</t>
         </is>
@@ -450,766 +455,1001 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Casco de seguridad tipo jockey blanco</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n"/>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="E2" s="1" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Casco de seguridad tipo jockey amarillo</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="E3" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Casco dieléctrico clase E</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="E4" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Barbiquejo de 3 puntas</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="E5" s="1" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Lentes de seguridad claros</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="E6" s="1" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Lentes de seguridad oscuros UV</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n"/>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="E7" s="1" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Antiparras antiempañantes</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n"/>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="E8" s="1" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Protector facial de policarbonato</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n"/>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="1" t="n"/>
+      <c r="D9" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="E9" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Careta de soldar fotosensible</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n"/>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="E10" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Protector auditivo tipo copa</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n"/>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="E11" s="1" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Protector auditivo endoform desechable</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n"/>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n">
         <v>400</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="E12" s="1" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>Respirador media cara doble vía</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n"/>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="1" t="n"/>
+      <c r="D13" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="E13" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Filtro mixto A1P2 (par)</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="E14" s="1" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Mascarilla desechable N95</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="1" t="n"/>
+      <c r="D15" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="E15" s="1" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Guantes de cabritilla</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="E16" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Guantes de cabritilla</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="E17" s="1" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Guantes de cabritilla</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="E18" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Guantes anticorte nivel 5</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="E19" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Guantes anticorte nivel 5</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="E20" s="1" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Guantes anticorte nivel 5</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="E21" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Guantes de nitrilo</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="E22" s="1" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>Guantes de nitrilo</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="E23" s="1" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Guantes dieléctricos clase 0</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="E24" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Zapato de seguridad dieléctrico</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="E25" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Zapato de seguridad dieléctrico</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="E26" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>Zapato de seguridad dieléctrico</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="D27" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="E27" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Zapato de seguridad dieléctrico</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="D28" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="E28" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Zapato de seguridad dieléctrico</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="D29" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="E29" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>Zapato de seguridad dieléctrico</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="E30" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Bota de agua con puntera de acero</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="D31" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="E31" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>Bota de agua con puntera de acero</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="D32" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="E32" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>Bota de agua con puntera de acero</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="D33" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="E33" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Chaleco reflectante geólogo</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="E34" s="1" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Chaleco reflectante geólogo</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="D35" s="1" t="n">
+      <c r="E35" s="1" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>Chaleco reflectante geólogo</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="D36" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="D36" s="1" t="n">
+      <c r="E36" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>Buzo desechable tipo Tyvek</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="D37" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="D37" s="1" t="n">
+      <c r="E37" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>Buzo desechable tipo Tyvek</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="D38" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D38" s="1" t="n">
+      <c r="E38" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>Parka térmica alta visibilidad</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="D39" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="D39" s="1" t="n">
+      <c r="E39" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Parka térmica alta visibilidad</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="D40" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D40" s="1" t="n">
+      <c r="E40" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>Parka térmica alta visibilidad</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="D41" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D41" s="1" t="n">
+      <c r="E41" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>Coleto de cuero para soldador</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n"/>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="1" t="n"/>
+      <c r="D42" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D42" s="1" t="n">
+      <c r="E42" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Arnés de seguridad cuerpo completo</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n"/>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="1" t="n"/>
+      <c r="D43" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="D43" s="1" t="n">
+      <c r="E43" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Cola de vida doble con absorbedor</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n"/>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="1" t="n"/>
+      <c r="D44" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="D44" s="1" t="n">
+      <c r="E44" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>Línea de vida retráctil 6 m</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n"/>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="1" t="n"/>
+      <c r="D45" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D45" s="1" t="n">
+      <c r="E45" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Malloco</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>Bloqueador solar FPS 50 (200 ml)</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n"/>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="1" t="n"/>
+      <c r="D46" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="D46" s="1" t="n">
+      <c r="E46" s="1" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Las Encinas</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Rodilleras de gel</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n"/>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="1" t="n"/>
+      <c r="D47" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D47" s="1" t="n">
+      <c r="E47" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Lucerna</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Cinturón lumbar</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="D48" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D48" s="1" t="n">
+      <c r="E48" s="1" t="n">
         <v>4</v>
       </c>
     </row>
